--- a/templates/FAX送付状.xlsx
+++ b/templates/FAX送付状.xlsx
@@ -8,6 +8,7 @@
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
+    <sheet name="プルダウンリスト" sheetId="8" r:id="rId1"/>
     <sheet name="汎用" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -777,6 +778,109 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C08F5E-AAD4-4B08-9F5A-1DE6CD576990}">
+  <sheetPr>
+    <tabColor theme="7" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">株式会社ライズクリエイション</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">足立</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">株式会社イノベイト</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">倉本</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAKUTENKEN株式会社</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伊藤</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">坂田</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">篠田</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">進地</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">福本</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奥田</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中浦</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">坂口</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67DE6450-65E8-4FAC-8035-CD70268E372D}">
   <dimension ref="B1:Q42"/>

--- a/templates/FAX送付状.xlsx
+++ b/templates/FAX送付状.xlsx
@@ -809,7 +809,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">倉本</t>
+          <t xml:space="preserve">伊藤</t>
         </is>
       </c>
     </row>
@@ -821,58 +821,50 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">伊藤</t>
+          <t xml:space="preserve">坂田</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">坂田</t>
+          <t xml:space="preserve">篠田</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">篠田</t>
+          <t xml:space="preserve">福本</t>
         </is>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">進地</t>
+          <t xml:space="preserve">奥田</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">福本</t>
+          <t xml:space="preserve">中浦</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">奥田</t>
+          <t xml:space="preserve">岩永</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中浦</t>
-        </is>
-      </c>
+      <c r="B9"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">坂口</t>
-        </is>
-      </c>
+      <c r="B10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/templates/FAX送付状.xlsx
+++ b/templates/FAX送付状.xlsx
@@ -1006,11 +1006,7 @@
         </is>
       </c>
       <c r="L10" s="15"/>
-      <c r="M10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">株式会社ライズクリエイション</t>
-        </is>
-      </c>
+      <c r="M10" s="17"/>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
       <c r="P10" s="17"/>
@@ -1034,13 +1030,9 @@
         </is>
       </c>
       <c r="L12" s="15"/>
-      <c r="M12" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">経理財務部</t>
-        </is>
-      </c>
+      <c r="M12" s="16"/>
       <c r="N12" s="16"/>
-      <c r="O12" s="16" t="inlineStr"/>
+      <c r="O12" s="16"/>
       <c r="P12" s="16"/>
       <c r="Q12" s="3"/>
     </row>
@@ -1062,11 +1054,7 @@
         </is>
       </c>
       <c r="L14" s="15"/>
-      <c r="M14" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0742-90-1051</t>
-        </is>
-      </c>
+      <c r="M14" s="16"/>
       <c r="N14" s="16"/>
       <c r="O14" s="16"/>
       <c r="P14" s="16"/>
@@ -1090,11 +1078,7 @@
         </is>
       </c>
       <c r="L16" s="15"/>
-      <c r="M16" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0742-81-9671</t>
-        </is>
-      </c>
+      <c r="M16" s="16"/>
       <c r="N16" s="16"/>
       <c r="O16" s="16"/>
       <c r="P16" s="16"/>
